--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N100_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N100_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.37844636525533</v>
+        <v>8.023997534353992</v>
       </c>
       <c r="D2" t="n">
-        <v>51.31649339069705</v>
+        <v>8.338930175988271</v>
       </c>
       <c r="E2" t="n">
-        <v>15.43206513580857</v>
+        <v>2.507710584568892</v>
       </c>
       <c r="F2" t="n">
-        <v>15.81824543324833</v>
+        <v>2.570464882902853</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.18257885976657</v>
+        <v>8.317169064712068</v>
       </c>
       <c r="D3" t="n">
-        <v>49.19123679861869</v>
+        <v>7.993575979775537</v>
       </c>
       <c r="E3" t="n">
-        <v>15.43206513580857</v>
+        <v>2.507710584568892</v>
       </c>
       <c r="F3" t="n">
-        <v>15.81824543324833</v>
+        <v>2.570464882902853</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.8041764883549</v>
+        <v>2.080678679357672</v>
       </c>
       <c r="D4" t="n">
-        <v>13.39634751399351</v>
+        <v>2.176906471023946</v>
       </c>
       <c r="E4" t="n">
-        <v>15.43206513580857</v>
+        <v>2.507710584568892</v>
       </c>
       <c r="F4" t="n">
-        <v>15.81824543324833</v>
+        <v>2.570464882902853</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.20804020459929</v>
+        <v>6.858806533247384</v>
       </c>
       <c r="D5" t="n">
-        <v>26.83500424385785</v>
+        <v>4.360688189626901</v>
       </c>
       <c r="E5" t="n">
-        <v>15.43206513580857</v>
+        <v>2.507710584568892</v>
       </c>
       <c r="F5" t="n">
-        <v>15.81824543324833</v>
+        <v>2.570464882902853</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
